--- a/Bibsam_tidskriftslistor/scifree_data_royalmedicine_hybrid.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_royalmedicine_hybrid.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_2B87336F5F4D2A7E649C04A305E36DBFE368FBB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFD137C3-10D5-40E4-8837-D576B81DE1FB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E59C35-833B-4380-B243-C4F11599A34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="101">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Journal of Medical Biography</t>
   </si>
   <si>
-    <t>Post Reproductive Health</t>
-  </si>
-  <si>
     <t>Tropical Doctor</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>0268-3555</t>
   </si>
   <si>
-    <t>2053-3691</t>
-  </si>
-  <si>
     <t>3693-9330</t>
   </si>
   <si>
@@ -181,9 +175,6 @@
     <t>1758-1125</t>
   </si>
   <si>
-    <t>2053-3705</t>
-  </si>
-  <si>
     <t>2045-6441</t>
   </si>
   <si>
@@ -244,9 +235,6 @@
     <t>http://journals.sagepub.com/home/phl</t>
   </si>
   <si>
-    <t>http://journals.sagepub.com/home/min</t>
-  </si>
-  <si>
     <t>http://journals.sagepub.com/home/scm</t>
   </si>
   <si>
@@ -326,6 +314,15 @@
   </si>
   <si>
     <t>Vascular</t>
+  </si>
+  <si>
+    <t>2048-0040</t>
+  </si>
+  <si>
+    <t>JRSM Cardiovascular Disease</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/home/CVD</t>
   </si>
 </sst>
 </file>
@@ -381,16 +378,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EE8C77C-1D1D-4EBF-A0D3-A8F96B39C4F2}" name="Table1" displayName="Table1" ref="A1:G24" totalsRowShown="0">
-  <autoFilter ref="A1:G24" xr:uid="{9EE8C77C-1D1D-4EBF-A0D3-A8F96B39C4F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F337FDBF-ADC2-412D-BF1F-9E3864FE1919}" name="Table13" displayName="Table13" ref="A1:G24" totalsRowShown="0">
+  <autoFilter ref="A1:G24" xr:uid="{F337FDBF-ADC2-412D-BF1F-9E3864FE1919}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G24">
+    <sortCondition ref="D1:D24"/>
+  </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{CC116DCD-3D1E-4A4C-ABD3-A81E3AB5B5D8}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{0F443297-41C0-418B-B812-4385DDC61B87}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{41EBFF82-0437-408F-9682-5CA38A3182C9}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{6E47717C-0264-43D7-A24E-FCFBE13F40A9}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{52B52025-2DBA-46B7-9FBA-23DA4684DC01}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{0B29FF39-7358-4DC7-9E30-2DDC9E3BFDE3}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{67EEBCE1-8435-4FD9-970E-AD38C68C330A}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{41DBDA51-9824-4590-93E8-FF7D7A622150}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{5A712415-6565-4CCC-BF14-F34E0337106A}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{74D368D9-9091-44A4-A809-1D16A2B538B9}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{1EA90F27-1B4E-49D3-89A3-D2EB141554C7}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{01367B18-7464-45D7-818B-8A943843FB25}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{E7C955FD-441D-42E6-9BBD-1F4F30032BCA}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{8E9BCDC3-7CD0-4B4E-825F-F748BDC86050}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -658,17 +658,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB4A256-3743-4D21-8D3D-33F31DD2649A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3819B062-CCEB-44AE-9590-A58DD216303E}">
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" customWidth="1"/>
+    <col min="4" max="4" width="52.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -696,19 +691,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -719,19 +714,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -742,19 +737,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -765,19 +760,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -788,19 +783,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -811,19 +806,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -834,19 +829,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -857,19 +852,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -880,19 +875,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
@@ -903,19 +898,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -926,19 +921,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -949,19 +944,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -972,19 +967,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
         <v>8</v>
@@ -995,19 +990,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
         <v>8</v>
@@ -1018,19 +1010,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
         <v>8</v>
@@ -1041,19 +1033,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -1064,19 +1056,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
         <v>8</v>
@@ -1087,19 +1079,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
@@ -1110,19 +1102,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
         <v>8</v>
@@ -1133,19 +1125,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -1156,19 +1148,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -1179,19 +1171,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
@@ -1202,19 +1194,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
